--- a/Q5. Sort and Filtering.xlsx
+++ b/Q5. Sort and Filtering.xlsx
@@ -8,15 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\ExcleR\Excel Assignment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BCB20E8-F22B-46B0-A328-9C5AA13CA1D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC085D66-77DB-4DAA-A066-0E16E98694E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sort" sheetId="1" r:id="rId1"/>
     <sheet name="Filter" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
+    <sheet name="filter1" sheetId="4" r:id="rId4"/>
+    <sheet name="filter2" sheetId="5" r:id="rId5"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Filter!$C$6:$G$319</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -38,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1898" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2206" uniqueCount="20">
   <si>
     <t>Sort as per conditions and Copy paste the results, by adding a new sheet in this file. Plus Paste Screenshots of Sort Box.</t>
   </si>
@@ -6459,6 +6464,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="C1:N998"/>
   <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
@@ -6514,7 +6520,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="3:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="3:14" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C7" s="2">
         <v>1</v>
       </c>
@@ -6531,7 +6537,7 @@
         <v>108879</v>
       </c>
     </row>
-    <row r="8" spans="3:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="3:14" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C8" s="2">
         <v>2</v>
       </c>
@@ -6548,7 +6554,7 @@
         <v>165656</v>
       </c>
     </row>
-    <row r="9" spans="3:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="3:14" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C9" s="2">
         <v>3</v>
       </c>
@@ -6565,7 +6571,7 @@
         <v>25467</v>
       </c>
     </row>
-    <row r="10" spans="3:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="3:14" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C10" s="2">
         <v>4</v>
       </c>
@@ -6599,7 +6605,7 @@
         <v>135801</v>
       </c>
     </row>
-    <row r="12" spans="3:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="3:14" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C12" s="2">
         <v>6</v>
       </c>
@@ -6616,7 +6622,7 @@
         <v>247286</v>
       </c>
     </row>
-    <row r="13" spans="3:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="3:14" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C13" s="2">
         <v>7</v>
       </c>
@@ -6633,7 +6639,7 @@
         <v>191293</v>
       </c>
     </row>
-    <row r="14" spans="3:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="3:14" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C14" s="2">
         <v>8</v>
       </c>
@@ -6650,7 +6656,7 @@
         <v>36125</v>
       </c>
     </row>
-    <row r="15" spans="3:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="3:14" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C15" s="2">
         <v>9</v>
       </c>
@@ -6684,7 +6690,7 @@
         <v>-34980</v>
       </c>
     </row>
-    <row r="17" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C17" s="2">
         <v>11</v>
       </c>
@@ -6701,7 +6707,7 @@
         <v>72086</v>
       </c>
     </row>
-    <row r="18" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C18" s="2">
         <v>12</v>
       </c>
@@ -6718,7 +6724,7 @@
         <v>84660</v>
       </c>
     </row>
-    <row r="19" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C19" s="2">
         <v>13</v>
       </c>
@@ -6735,7 +6741,7 @@
         <v>201069</v>
       </c>
     </row>
-    <row r="20" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C20" s="2">
         <v>14</v>
       </c>
@@ -6752,7 +6758,7 @@
         <v>74221</v>
       </c>
     </row>
-    <row r="21" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C21" s="2">
         <v>15</v>
       </c>
@@ -6769,7 +6775,7 @@
         <v>155904</v>
       </c>
     </row>
-    <row r="22" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C22" s="2">
         <v>16</v>
       </c>
@@ -6786,7 +6792,7 @@
         <v>-37886</v>
       </c>
     </row>
-    <row r="23" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C23" s="2">
         <v>17</v>
       </c>
@@ -6803,7 +6809,7 @@
         <v>169991</v>
       </c>
     </row>
-    <row r="24" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C24" s="2">
         <v>18</v>
       </c>
@@ -6820,7 +6826,7 @@
         <v>207031</v>
       </c>
     </row>
-    <row r="25" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C25" s="2">
         <v>19</v>
       </c>
@@ -6837,7 +6843,7 @@
         <v>39668</v>
       </c>
     </row>
-    <row r="26" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C26" s="2">
         <v>20</v>
       </c>
@@ -6854,7 +6860,7 @@
         <v>180474</v>
       </c>
     </row>
-    <row r="27" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C27" s="2">
         <v>21</v>
       </c>
@@ -6871,7 +6877,7 @@
         <v>-7921</v>
       </c>
     </row>
-    <row r="28" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C28" s="2">
         <v>22</v>
       </c>
@@ -6905,7 +6911,7 @@
         <v>149617</v>
       </c>
     </row>
-    <row r="30" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C30" s="2">
         <v>24</v>
       </c>
@@ -6939,7 +6945,7 @@
         <v>60921</v>
       </c>
     </row>
-    <row r="32" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C32" s="2">
         <v>26</v>
       </c>
@@ -6956,7 +6962,7 @@
         <v>180969</v>
       </c>
     </row>
-    <row r="33" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C33" s="2">
         <v>27</v>
       </c>
@@ -6990,7 +6996,7 @@
         <v>12909</v>
       </c>
     </row>
-    <row r="35" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C35" s="2">
         <v>29</v>
       </c>
@@ -7041,7 +7047,7 @@
         <v>87532</v>
       </c>
     </row>
-    <row r="38" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C38" s="2">
         <v>32</v>
       </c>
@@ -7092,7 +7098,7 @@
         <v>57399</v>
       </c>
     </row>
-    <row r="41" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C41" s="2">
         <v>35</v>
       </c>
@@ -7126,7 +7132,7 @@
         <v>55010</v>
       </c>
     </row>
-    <row r="43" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C43" s="2">
         <v>37</v>
       </c>
@@ -7143,7 +7149,7 @@
         <v>142874</v>
       </c>
     </row>
-    <row r="44" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C44" s="2">
         <v>38</v>
       </c>
@@ -7160,7 +7166,7 @@
         <v>166353</v>
       </c>
     </row>
-    <row r="45" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C45" s="2">
         <v>39</v>
       </c>
@@ -7194,7 +7200,7 @@
         <v>86220</v>
       </c>
     </row>
-    <row r="47" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C47" s="2">
         <v>41</v>
       </c>
@@ -7211,7 +7217,7 @@
         <v>27542</v>
       </c>
     </row>
-    <row r="48" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C48" s="2">
         <v>42</v>
       </c>
@@ -7245,7 +7251,7 @@
         <v>17711</v>
       </c>
     </row>
-    <row r="50" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C50" s="2">
         <v>44</v>
       </c>
@@ -7262,7 +7268,7 @@
         <v>18670</v>
       </c>
     </row>
-    <row r="51" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C51" s="2">
         <v>45</v>
       </c>
@@ -7279,7 +7285,7 @@
         <v>87460</v>
       </c>
     </row>
-    <row r="52" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C52" s="2">
         <v>46</v>
       </c>
@@ -7296,7 +7302,7 @@
         <v>17043</v>
       </c>
     </row>
-    <row r="53" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C53" s="2">
         <v>47</v>
       </c>
@@ -7313,7 +7319,7 @@
         <v>48442</v>
       </c>
     </row>
-    <row r="54" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C54" s="2">
         <v>48</v>
       </c>
@@ -7330,7 +7336,7 @@
         <v>175220</v>
       </c>
     </row>
-    <row r="55" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C55" s="2">
         <v>49</v>
       </c>
@@ -7347,7 +7353,7 @@
         <v>146394</v>
       </c>
     </row>
-    <row r="56" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C56" s="2">
         <v>50</v>
       </c>
@@ -7364,7 +7370,7 @@
         <v>158679</v>
       </c>
     </row>
-    <row r="57" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C57" s="2">
         <v>51</v>
       </c>
@@ -7398,7 +7404,7 @@
         <v>5850</v>
       </c>
     </row>
-    <row r="59" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C59" s="2">
         <v>53</v>
       </c>
@@ -7415,7 +7421,7 @@
         <v>-15140</v>
       </c>
     </row>
-    <row r="60" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C60" s="2">
         <v>54</v>
       </c>
@@ -7449,7 +7455,7 @@
         <v>131983</v>
       </c>
     </row>
-    <row r="62" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C62" s="2">
         <v>56</v>
       </c>
@@ -7483,7 +7489,7 @@
         <v>96209</v>
       </c>
     </row>
-    <row r="64" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C64" s="2">
         <v>58</v>
       </c>
@@ -7500,7 +7506,7 @@
         <v>134977</v>
       </c>
     </row>
-    <row r="65" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C65" s="2">
         <v>59</v>
       </c>
@@ -7517,7 +7523,7 @@
         <v>59423</v>
       </c>
     </row>
-    <row r="66" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C66" s="2">
         <v>60</v>
       </c>
@@ -7551,7 +7557,7 @@
         <v>19225</v>
       </c>
     </row>
-    <row r="68" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C68" s="2">
         <v>62</v>
       </c>
@@ -7568,7 +7574,7 @@
         <v>150851</v>
       </c>
     </row>
-    <row r="69" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C69" s="2">
         <v>63</v>
       </c>
@@ -7585,7 +7591,7 @@
         <v>7110</v>
       </c>
     </row>
-    <row r="70" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C70" s="2">
         <v>64</v>
       </c>
@@ -7602,7 +7608,7 @@
         <v>259896</v>
       </c>
     </row>
-    <row r="71" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C71" s="2">
         <v>65</v>
       </c>
@@ -7619,7 +7625,7 @@
         <v>222162</v>
       </c>
     </row>
-    <row r="72" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C72" s="2">
         <v>66</v>
       </c>
@@ -7636,7 +7642,7 @@
         <v>5652</v>
       </c>
     </row>
-    <row r="73" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C73" s="2">
         <v>67</v>
       </c>
@@ -7653,7 +7659,7 @@
         <v>173392</v>
       </c>
     </row>
-    <row r="74" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C74" s="2">
         <v>68</v>
       </c>
@@ -7670,7 +7676,7 @@
         <v>230726</v>
       </c>
     </row>
-    <row r="75" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C75" s="2">
         <v>69</v>
       </c>
@@ -7687,7 +7693,7 @@
         <v>154630</v>
       </c>
     </row>
-    <row r="76" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C76" s="2">
         <v>70</v>
       </c>
@@ -7704,7 +7710,7 @@
         <v>161165</v>
       </c>
     </row>
-    <row r="77" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C77" s="2">
         <v>71</v>
       </c>
@@ -7721,7 +7727,7 @@
         <v>6105</v>
       </c>
     </row>
-    <row r="78" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C78" s="2">
         <v>72</v>
       </c>
@@ -7738,7 +7744,7 @@
         <v>34334</v>
       </c>
     </row>
-    <row r="79" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C79" s="2">
         <v>73</v>
       </c>
@@ -7755,7 +7761,7 @@
         <v>8406</v>
       </c>
     </row>
-    <row r="80" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C80" s="2">
         <v>74</v>
       </c>
@@ -7823,7 +7829,7 @@
         <v>229218</v>
       </c>
     </row>
-    <row r="84" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C84" s="2">
         <v>78</v>
       </c>
@@ -7840,7 +7846,7 @@
         <v>82968</v>
       </c>
     </row>
-    <row r="85" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C85" s="2">
         <v>79</v>
       </c>
@@ -7857,7 +7863,7 @@
         <v>234786</v>
       </c>
     </row>
-    <row r="86" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C86" s="2">
         <v>80</v>
       </c>
@@ -7908,7 +7914,7 @@
         <v>85536</v>
       </c>
     </row>
-    <row r="89" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C89" s="2">
         <v>83</v>
       </c>
@@ -7959,7 +7965,7 @@
         <v>124717</v>
       </c>
     </row>
-    <row r="92" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C92" s="2">
         <v>86</v>
       </c>
@@ -7993,7 +7999,7 @@
         <v>99343</v>
       </c>
     </row>
-    <row r="94" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C94" s="2">
         <v>88</v>
       </c>
@@ -8010,7 +8016,7 @@
         <v>41318</v>
       </c>
     </row>
-    <row r="95" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C95" s="2">
         <v>89</v>
       </c>
@@ -8027,7 +8033,7 @@
         <v>211082</v>
       </c>
     </row>
-    <row r="96" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C96" s="2">
         <v>90</v>
       </c>
@@ -8044,7 +8050,7 @@
         <v>8675</v>
       </c>
     </row>
-    <row r="97" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C97" s="2">
         <v>91</v>
       </c>
@@ -8061,7 +8067,7 @@
         <v>132363</v>
       </c>
     </row>
-    <row r="98" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C98" s="2">
         <v>92</v>
       </c>
@@ -8078,7 +8084,7 @@
         <v>130275</v>
       </c>
     </row>
-    <row r="99" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C99" s="2">
         <v>93</v>
       </c>
@@ -8095,7 +8101,7 @@
         <v>174302</v>
       </c>
     </row>
-    <row r="100" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C100" s="2">
         <v>94</v>
       </c>
@@ -8112,7 +8118,7 @@
         <v>126174</v>
       </c>
     </row>
-    <row r="101" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C101" s="2">
         <v>95</v>
       </c>
@@ -8129,7 +8135,7 @@
         <v>13328</v>
       </c>
     </row>
-    <row r="102" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C102" s="2">
         <v>96</v>
       </c>
@@ -8146,7 +8152,7 @@
         <v>48808</v>
       </c>
     </row>
-    <row r="103" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C103" s="2">
         <v>97</v>
       </c>
@@ -8163,7 +8169,7 @@
         <v>258583</v>
       </c>
     </row>
-    <row r="104" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C104" s="2">
         <v>98</v>
       </c>
@@ -8214,7 +8220,7 @@
         <v>109849</v>
       </c>
     </row>
-    <row r="107" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C107" s="2">
         <v>101</v>
       </c>
@@ -8248,7 +8254,7 @@
         <v>219148</v>
       </c>
     </row>
-    <row r="109" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C109" s="2">
         <v>103</v>
       </c>
@@ -8265,7 +8271,7 @@
         <v>187979</v>
       </c>
     </row>
-    <row r="110" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C110" s="2">
         <v>104</v>
       </c>
@@ -8282,7 +8288,7 @@
         <v>91931</v>
       </c>
     </row>
-    <row r="111" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C111" s="2">
         <v>105</v>
       </c>
@@ -8316,7 +8322,7 @@
         <v>213879</v>
       </c>
     </row>
-    <row r="113" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C113" s="2">
         <v>107</v>
       </c>
@@ -8333,7 +8339,7 @@
         <v>7298</v>
       </c>
     </row>
-    <row r="114" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C114" s="2">
         <v>108</v>
       </c>
@@ -8350,7 +8356,7 @@
         <v>1661</v>
       </c>
     </row>
-    <row r="115" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C115" s="2">
         <v>109</v>
       </c>
@@ -8367,7 +8373,7 @@
         <v>13845</v>
       </c>
     </row>
-    <row r="116" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C116" s="2">
         <v>110</v>
       </c>
@@ -8401,7 +8407,7 @@
         <v>36547</v>
       </c>
     </row>
-    <row r="118" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C118" s="2">
         <v>112</v>
       </c>
@@ -8435,7 +8441,7 @@
         <v>26819</v>
       </c>
     </row>
-    <row r="120" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C120" s="2">
         <v>114</v>
       </c>
@@ -8469,7 +8475,7 @@
         <v>220591</v>
       </c>
     </row>
-    <row r="122" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C122" s="2">
         <v>116</v>
       </c>
@@ -8486,7 +8492,7 @@
         <v>216695</v>
       </c>
     </row>
-    <row r="123" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C123" s="2">
         <v>117</v>
       </c>
@@ -8571,7 +8577,7 @@
         <v>209590</v>
       </c>
     </row>
-    <row r="128" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C128" s="2">
         <v>122</v>
       </c>
@@ -8588,7 +8594,7 @@
         <v>135311</v>
       </c>
     </row>
-    <row r="129" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C129" s="2">
         <v>123</v>
       </c>
@@ -8605,7 +8611,7 @@
         <v>115261</v>
       </c>
     </row>
-    <row r="130" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C130" s="2">
         <v>124</v>
       </c>
@@ -8622,7 +8628,7 @@
         <v>220171</v>
       </c>
     </row>
-    <row r="131" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C131" s="2">
         <v>125</v>
       </c>
@@ -8639,7 +8645,7 @@
         <v>9682</v>
       </c>
     </row>
-    <row r="132" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C132" s="2">
         <v>126</v>
       </c>
@@ -8656,7 +8662,7 @@
         <v>81048</v>
       </c>
     </row>
-    <row r="133" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C133" s="2">
         <v>127</v>
       </c>
@@ -8673,7 +8679,7 @@
         <v>155266</v>
       </c>
     </row>
-    <row r="134" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C134" s="2">
         <v>128</v>
       </c>
@@ -8690,7 +8696,7 @@
         <v>24879</v>
       </c>
     </row>
-    <row r="135" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C135" s="2">
         <v>129</v>
       </c>
@@ -8707,7 +8713,7 @@
         <v>24838</v>
       </c>
     </row>
-    <row r="136" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C136" s="2">
         <v>130</v>
       </c>
@@ -8724,7 +8730,7 @@
         <v>105602</v>
       </c>
     </row>
-    <row r="137" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C137" s="2">
         <v>131</v>
       </c>
@@ -8758,7 +8764,7 @@
         <v>27327</v>
       </c>
     </row>
-    <row r="139" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C139" s="2">
         <v>133</v>
       </c>
@@ -8775,7 +8781,7 @@
         <v>142596</v>
       </c>
     </row>
-    <row r="140" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C140" s="2">
         <v>134</v>
       </c>
@@ -8792,7 +8798,7 @@
         <v>165992</v>
       </c>
     </row>
-    <row r="141" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C141" s="2">
         <v>135</v>
       </c>
@@ -8809,7 +8815,7 @@
         <v>129328</v>
       </c>
     </row>
-    <row r="142" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C142" s="2">
         <v>136</v>
       </c>
@@ -8826,7 +8832,7 @@
         <v>86460</v>
       </c>
     </row>
-    <row r="143" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C143" s="2">
         <v>137</v>
       </c>
@@ -8877,7 +8883,7 @@
         <v>217075</v>
       </c>
     </row>
-    <row r="146" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C146" s="2">
         <v>140</v>
       </c>
@@ -8894,7 +8900,7 @@
         <v>56810</v>
       </c>
     </row>
-    <row r="147" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C147" s="2">
         <v>141</v>
       </c>
@@ -8928,7 +8934,7 @@
         <v>217962</v>
       </c>
     </row>
-    <row r="149" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C149" s="2">
         <v>143</v>
       </c>
@@ -8945,7 +8951,7 @@
         <v>166824</v>
       </c>
     </row>
-    <row r="150" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C150" s="2">
         <v>144</v>
       </c>
@@ -8979,7 +8985,7 @@
         <v>64755</v>
       </c>
     </row>
-    <row r="152" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C152" s="2">
         <v>146</v>
       </c>
@@ -8996,7 +9002,7 @@
         <v>8950</v>
       </c>
     </row>
-    <row r="153" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C153" s="2">
         <v>147</v>
       </c>
@@ -9030,7 +9036,7 @@
         <v>191733</v>
       </c>
     </row>
-    <row r="155" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C155" s="2">
         <v>149</v>
       </c>
@@ -9081,7 +9087,7 @@
         <v>173616</v>
       </c>
     </row>
-    <row r="158" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C158" s="2">
         <v>152</v>
       </c>
@@ -9098,7 +9104,7 @@
         <v>168122</v>
       </c>
     </row>
-    <row r="159" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C159" s="2">
         <v>153</v>
       </c>
@@ -9115,7 +9121,7 @@
         <v>151084</v>
       </c>
     </row>
-    <row r="160" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C160" s="2">
         <v>154</v>
       </c>
@@ -9132,7 +9138,7 @@
         <v>247904</v>
       </c>
     </row>
-    <row r="161" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C161" s="2">
         <v>155</v>
       </c>
@@ -9149,7 +9155,7 @@
         <v>33876</v>
       </c>
     </row>
-    <row r="162" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C162" s="2">
         <v>156</v>
       </c>
@@ -9166,7 +9172,7 @@
         <v>95791</v>
       </c>
     </row>
-    <row r="163" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C163" s="2">
         <v>157</v>
       </c>
@@ -9183,7 +9189,7 @@
         <v>201120</v>
       </c>
     </row>
-    <row r="164" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C164" s="2">
         <v>158</v>
       </c>
@@ -9200,7 +9206,7 @@
         <v>196137</v>
       </c>
     </row>
-    <row r="165" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C165" s="2">
         <v>159</v>
       </c>
@@ -9217,7 +9223,7 @@
         <v>6345</v>
       </c>
     </row>
-    <row r="166" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C166" s="2">
         <v>160</v>
       </c>
@@ -9234,7 +9240,7 @@
         <v>60394</v>
       </c>
     </row>
-    <row r="167" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C167" s="2">
         <v>161</v>
       </c>
@@ -9251,7 +9257,7 @@
         <v>208053</v>
       </c>
     </row>
-    <row r="168" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C168" s="2">
         <v>162</v>
       </c>
@@ -9268,7 +9274,7 @@
         <v>216555</v>
       </c>
     </row>
-    <row r="169" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C169" s="2">
         <v>163</v>
       </c>
@@ -9285,7 +9291,7 @@
         <v>30219</v>
       </c>
     </row>
-    <row r="170" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C170" s="2">
         <v>164</v>
       </c>
@@ -9302,7 +9308,7 @@
         <v>112636</v>
       </c>
     </row>
-    <row r="171" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C171" s="2">
         <v>165</v>
       </c>
@@ -9336,7 +9342,7 @@
         <v>23560</v>
       </c>
     </row>
-    <row r="173" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C173" s="2">
         <v>167</v>
       </c>
@@ -9370,7 +9376,7 @@
         <v>185869</v>
       </c>
     </row>
-    <row r="175" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C175" s="2">
         <v>169</v>
       </c>
@@ -9387,7 +9393,7 @@
         <v>73394</v>
       </c>
     </row>
-    <row r="176" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C176" s="2">
         <v>170</v>
       </c>
@@ -9404,7 +9410,7 @@
         <v>254580</v>
       </c>
     </row>
-    <row r="177" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C177" s="2">
         <v>171</v>
       </c>
@@ -9421,7 +9427,7 @@
         <v>175018</v>
       </c>
     </row>
-    <row r="178" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C178" s="2">
         <v>172</v>
       </c>
@@ -9438,7 +9444,7 @@
         <v>248756</v>
       </c>
     </row>
-    <row r="179" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C179" s="2">
         <v>173</v>
       </c>
@@ -9455,7 +9461,7 @@
         <v>22305</v>
       </c>
     </row>
-    <row r="180" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C180" s="2">
         <v>174</v>
       </c>
@@ -9472,7 +9478,7 @@
         <v>5187</v>
       </c>
     </row>
-    <row r="181" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C181" s="2">
         <v>175</v>
       </c>
@@ -9489,7 +9495,7 @@
         <v>100486</v>
       </c>
     </row>
-    <row r="182" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C182" s="2">
         <v>176</v>
       </c>
@@ -9506,7 +9512,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="183" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C183" s="2">
         <v>177</v>
       </c>
@@ -9523,7 +9529,7 @@
         <v>61230</v>
       </c>
     </row>
-    <row r="184" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C184" s="2">
         <v>178</v>
       </c>
@@ -9540,7 +9546,7 @@
         <v>29435</v>
       </c>
     </row>
-    <row r="185" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C185" s="2">
         <v>179</v>
       </c>
@@ -9557,7 +9563,7 @@
         <v>74022</v>
       </c>
     </row>
-    <row r="186" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C186" s="2">
         <v>180</v>
       </c>
@@ -9574,7 +9580,7 @@
         <v>124153</v>
       </c>
     </row>
-    <row r="187" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C187" s="2">
         <v>181</v>
       </c>
@@ -9591,7 +9597,7 @@
         <v>225220</v>
       </c>
     </row>
-    <row r="188" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C188" s="2">
         <v>182</v>
       </c>
@@ -9608,7 +9614,7 @@
         <v>164464</v>
       </c>
     </row>
-    <row r="189" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C189" s="2">
         <v>183</v>
       </c>
@@ -9625,7 +9631,7 @@
         <v>145328</v>
       </c>
     </row>
-    <row r="190" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C190" s="2">
         <v>184</v>
       </c>
@@ -9642,7 +9648,7 @@
         <v>189847</v>
       </c>
     </row>
-    <row r="191" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C191" s="2">
         <v>185</v>
       </c>
@@ -9659,7 +9665,7 @@
         <v>240648</v>
       </c>
     </row>
-    <row r="192" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C192" s="2">
         <v>186</v>
       </c>
@@ -9710,7 +9716,7 @@
         <v>13179</v>
       </c>
     </row>
-    <row r="195" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C195" s="2">
         <v>189</v>
       </c>
@@ -9727,7 +9733,7 @@
         <v>210276</v>
       </c>
     </row>
-    <row r="196" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C196" s="2">
         <v>190</v>
       </c>
@@ -9744,7 +9750,7 @@
         <v>86142</v>
       </c>
     </row>
-    <row r="197" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C197" s="2">
         <v>191</v>
       </c>
@@ -9778,7 +9784,7 @@
         <v>86843</v>
       </c>
     </row>
-    <row r="199" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C199" s="2">
         <v>193</v>
       </c>
@@ -9795,7 +9801,7 @@
         <v>-21877</v>
       </c>
     </row>
-    <row r="200" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C200" s="2">
         <v>194</v>
       </c>
@@ -9812,7 +9818,7 @@
         <v>95623</v>
       </c>
     </row>
-    <row r="201" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C201" s="2">
         <v>195</v>
       </c>
@@ -9846,7 +9852,7 @@
         <v>103592</v>
       </c>
     </row>
-    <row r="203" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C203" s="2">
         <v>197</v>
       </c>
@@ -9880,7 +9886,7 @@
         <v>138473</v>
       </c>
     </row>
-    <row r="205" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C205" s="2">
         <v>199</v>
       </c>
@@ -9948,7 +9954,7 @@
         <v>23010</v>
       </c>
     </row>
-    <row r="209" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C209" s="2">
         <v>203</v>
       </c>
@@ -9965,7 +9971,7 @@
         <v>71529</v>
       </c>
     </row>
-    <row r="210" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C210" s="2">
         <v>204</v>
       </c>
@@ -9982,7 +9988,7 @@
         <v>39494</v>
       </c>
     </row>
-    <row r="211" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C211" s="2">
         <v>205</v>
       </c>
@@ -10033,7 +10039,7 @@
         <v>258051</v>
       </c>
     </row>
-    <row r="214" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C214" s="2">
         <v>208</v>
       </c>
@@ -10050,7 +10056,7 @@
         <v>6460</v>
       </c>
     </row>
-    <row r="215" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C215" s="2">
         <v>209</v>
       </c>
@@ -10067,7 +10073,7 @@
         <v>114470</v>
       </c>
     </row>
-    <row r="216" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C216" s="2">
         <v>210</v>
       </c>
@@ -10101,7 +10107,7 @@
         <v>160752</v>
       </c>
     </row>
-    <row r="218" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C218" s="2">
         <v>212</v>
       </c>
@@ -10118,7 +10124,7 @@
         <v>1365</v>
       </c>
     </row>
-    <row r="219" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C219" s="2">
         <v>213</v>
       </c>
@@ -10135,7 +10141,7 @@
         <v>54633</v>
       </c>
     </row>
-    <row r="220" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C220" s="2">
         <v>214</v>
       </c>
@@ -10152,7 +10158,7 @@
         <v>130437</v>
       </c>
     </row>
-    <row r="221" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C221" s="2">
         <v>215</v>
       </c>
@@ -10186,7 +10192,7 @@
         <v>110965</v>
       </c>
     </row>
-    <row r="223" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C223" s="2">
         <v>217</v>
       </c>
@@ -10203,7 +10209,7 @@
         <v>159478</v>
       </c>
     </row>
-    <row r="224" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C224" s="2">
         <v>218</v>
       </c>
@@ -10220,7 +10226,7 @@
         <v>96983</v>
       </c>
     </row>
-    <row r="225" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C225" s="2">
         <v>219</v>
       </c>
@@ -10237,7 +10243,7 @@
         <v>15238</v>
       </c>
     </row>
-    <row r="226" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C226" s="2">
         <v>220</v>
       </c>
@@ -10254,7 +10260,7 @@
         <v>89649</v>
       </c>
     </row>
-    <row r="227" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C227" s="2">
         <v>221</v>
       </c>
@@ -10271,7 +10277,7 @@
         <v>42319</v>
       </c>
     </row>
-    <row r="228" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C228" s="2">
         <v>222</v>
       </c>
@@ -10305,7 +10311,7 @@
         <v>78549</v>
       </c>
     </row>
-    <row r="230" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C230" s="2">
         <v>224</v>
       </c>
@@ -10322,7 +10328,7 @@
         <v>1696</v>
       </c>
     </row>
-    <row r="231" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C231" s="2">
         <v>225</v>
       </c>
@@ -10339,7 +10345,7 @@
         <v>252387</v>
       </c>
     </row>
-    <row r="232" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C232" s="2">
         <v>226</v>
       </c>
@@ -10356,7 +10362,7 @@
         <v>27849</v>
       </c>
     </row>
-    <row r="233" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C233" s="2">
         <v>227</v>
       </c>
@@ -10373,7 +10379,7 @@
         <v>173334</v>
       </c>
     </row>
-    <row r="234" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C234" s="2">
         <v>228</v>
       </c>
@@ -10390,7 +10396,7 @@
         <v>221658</v>
       </c>
     </row>
-    <row r="235" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C235" s="2">
         <v>229</v>
       </c>
@@ -10407,7 +10413,7 @@
         <v>12709</v>
       </c>
     </row>
-    <row r="236" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C236" s="2">
         <v>230</v>
       </c>
@@ -10424,7 +10430,7 @@
         <v>6845</v>
       </c>
     </row>
-    <row r="237" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C237" s="2">
         <v>231</v>
       </c>
@@ -10475,7 +10481,7 @@
         <v>12894</v>
       </c>
     </row>
-    <row r="240" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C240" s="2">
         <v>234</v>
       </c>
@@ -10492,7 +10498,7 @@
         <v>236531</v>
       </c>
     </row>
-    <row r="241" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C241" s="2">
         <v>235</v>
       </c>
@@ -10509,7 +10515,7 @@
         <v>128249</v>
       </c>
     </row>
-    <row r="242" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C242" s="2">
         <v>236</v>
       </c>
@@ -10526,7 +10532,7 @@
         <v>210352</v>
       </c>
     </row>
-    <row r="243" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C243" s="2">
         <v>237</v>
       </c>
@@ -10543,7 +10549,7 @@
         <v>133951</v>
       </c>
     </row>
-    <row r="244" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C244" s="2">
         <v>238</v>
       </c>
@@ -10577,7 +10583,7 @@
         <v>256402</v>
       </c>
     </row>
-    <row r="246" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C246" s="2">
         <v>240</v>
       </c>
@@ -10594,7 +10600,7 @@
         <v>151301</v>
       </c>
     </row>
-    <row r="247" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C247" s="2">
         <v>241</v>
       </c>
@@ -10611,7 +10617,7 @@
         <v>74813</v>
       </c>
     </row>
-    <row r="248" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C248" s="2">
         <v>242</v>
       </c>
@@ -10628,7 +10634,7 @@
         <v>161532</v>
       </c>
     </row>
-    <row r="249" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C249" s="2">
         <v>243</v>
       </c>
@@ -10645,7 +10651,7 @@
         <v>63494</v>
       </c>
     </row>
-    <row r="250" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C250" s="2">
         <v>244</v>
       </c>
@@ -10662,7 +10668,7 @@
         <v>8463</v>
       </c>
     </row>
-    <row r="251" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C251" s="2">
         <v>245</v>
       </c>
@@ -10679,7 +10685,7 @@
         <v>9630</v>
       </c>
     </row>
-    <row r="252" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C252" s="2">
         <v>246</v>
       </c>
@@ -10747,7 +10753,7 @@
         <v>23250</v>
       </c>
     </row>
-    <row r="256" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C256" s="2">
         <v>250</v>
       </c>
@@ -10781,7 +10787,7 @@
         <v>52513</v>
       </c>
     </row>
-    <row r="258" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C258" s="2">
         <v>252</v>
       </c>
@@ -10798,7 +10804,7 @@
         <v>25860</v>
       </c>
     </row>
-    <row r="259" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C259" s="2">
         <v>253</v>
       </c>
@@ -10832,7 +10838,7 @@
         <v>159745</v>
       </c>
     </row>
-    <row r="261" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C261" s="2">
         <v>255</v>
       </c>
@@ -10849,7 +10855,7 @@
         <v>6256</v>
       </c>
     </row>
-    <row r="262" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C262" s="2">
         <v>256</v>
       </c>
@@ -10883,7 +10889,7 @@
         <v>7382</v>
       </c>
     </row>
-    <row r="264" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C264" s="2">
         <v>258</v>
       </c>
@@ -10900,7 +10906,7 @@
         <v>26172</v>
       </c>
     </row>
-    <row r="265" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C265" s="2">
         <v>259</v>
       </c>
@@ -10917,7 +10923,7 @@
         <v>223295</v>
       </c>
     </row>
-    <row r="266" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C266" s="2">
         <v>260</v>
       </c>
@@ -10934,7 +10940,7 @@
         <v>213069</v>
       </c>
     </row>
-    <row r="267" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C267" s="2">
         <v>261</v>
       </c>
@@ -10951,7 +10957,7 @@
         <v>7190</v>
       </c>
     </row>
-    <row r="268" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C268" s="2">
         <v>262</v>
       </c>
@@ -11019,7 +11025,7 @@
         <v>55991</v>
       </c>
     </row>
-    <row r="272" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C272" s="2">
         <v>266</v>
       </c>
@@ -11036,7 +11042,7 @@
         <v>134107</v>
       </c>
     </row>
-    <row r="273" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C273" s="2">
         <v>267</v>
       </c>
@@ -11053,7 +11059,7 @@
         <v>104379</v>
       </c>
     </row>
-    <row r="274" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C274" s="2">
         <v>268</v>
       </c>
@@ -11070,7 +11076,7 @@
         <v>22810</v>
       </c>
     </row>
-    <row r="275" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C275" s="2">
         <v>269</v>
       </c>
@@ -11087,7 +11093,7 @@
         <v>28289</v>
       </c>
     </row>
-    <row r="276" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C276" s="2">
         <v>270</v>
       </c>
@@ -11104,7 +11110,7 @@
         <v>65162</v>
       </c>
     </row>
-    <row r="277" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C277" s="2">
         <v>271</v>
       </c>
@@ -11121,7 +11127,7 @@
         <v>201340</v>
       </c>
     </row>
-    <row r="278" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C278" s="2">
         <v>272</v>
       </c>
@@ -11155,7 +11161,7 @@
         <v>104422</v>
       </c>
     </row>
-    <row r="280" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C280" s="2">
         <v>274</v>
       </c>
@@ -11172,7 +11178,7 @@
         <v>100956</v>
       </c>
     </row>
-    <row r="281" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C281" s="2">
         <v>275</v>
       </c>
@@ -11206,7 +11212,7 @@
         <v>59920</v>
       </c>
     </row>
-    <row r="283" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C283" s="2">
         <v>277</v>
       </c>
@@ -11223,7 +11229,7 @@
         <v>163127</v>
       </c>
     </row>
-    <row r="284" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C284" s="2">
         <v>278</v>
       </c>
@@ -11240,7 +11246,7 @@
         <v>232472</v>
       </c>
     </row>
-    <row r="285" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C285" s="2">
         <v>279</v>
       </c>
@@ -11257,7 +11263,7 @@
         <v>28110</v>
       </c>
     </row>
-    <row r="286" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C286" s="2">
         <v>280</v>
       </c>
@@ -11274,7 +11280,7 @@
         <v>40778</v>
       </c>
     </row>
-    <row r="287" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C287" s="2">
         <v>281</v>
       </c>
@@ -11308,7 +11314,7 @@
         <v>216458</v>
       </c>
     </row>
-    <row r="289" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C289" s="2">
         <v>283</v>
       </c>
@@ -11325,7 +11331,7 @@
         <v>39973</v>
       </c>
     </row>
-    <row r="290" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C290" s="2">
         <v>284</v>
       </c>
@@ -11342,7 +11348,7 @@
         <v>195638</v>
       </c>
     </row>
-    <row r="291" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C291" s="2">
         <v>285</v>
       </c>
@@ -11359,7 +11365,7 @@
         <v>256329</v>
       </c>
     </row>
-    <row r="292" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C292" s="2">
         <v>286</v>
       </c>
@@ -11376,7 +11382,7 @@
         <v>11238</v>
       </c>
     </row>
-    <row r="293" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C293" s="2">
         <v>287</v>
       </c>
@@ -11410,7 +11416,7 @@
         <v>226327</v>
       </c>
     </row>
-    <row r="295" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C295" s="2">
         <v>289</v>
       </c>
@@ -11427,7 +11433,7 @@
         <v>192728</v>
       </c>
     </row>
-    <row r="296" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C296" s="2">
         <v>290</v>
       </c>
@@ -11461,7 +11467,7 @@
         <v>12156</v>
       </c>
     </row>
-    <row r="298" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C298" s="2">
         <v>292</v>
       </c>
@@ -11478,7 +11484,7 @@
         <v>11682</v>
       </c>
     </row>
-    <row r="299" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C299" s="2">
         <v>293</v>
       </c>
@@ -11495,7 +11501,7 @@
         <v>161110</v>
       </c>
     </row>
-    <row r="300" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C300" s="2">
         <v>294</v>
       </c>
@@ -11512,7 +11518,7 @@
         <v>155535</v>
       </c>
     </row>
-    <row r="301" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C301" s="2">
         <v>295</v>
       </c>
@@ -11529,7 +11535,7 @@
         <v>223894</v>
       </c>
     </row>
-    <row r="302" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C302" s="2">
         <v>296</v>
       </c>
@@ -11546,7 +11552,7 @@
         <v>22839</v>
       </c>
     </row>
-    <row r="303" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C303" s="2">
         <v>297</v>
       </c>
@@ -11580,7 +11586,7 @@
         <v>98246</v>
       </c>
     </row>
-    <row r="305" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C305" s="2">
         <v>299</v>
       </c>
@@ -11614,7 +11620,7 @@
         <v>74093</v>
       </c>
     </row>
-    <row r="307" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C307" s="2">
         <v>301</v>
       </c>
@@ -11648,7 +11654,7 @@
         <v>75634</v>
       </c>
     </row>
-    <row r="309" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C309" s="2">
         <v>303</v>
       </c>
@@ -11665,7 +11671,7 @@
         <v>-11610</v>
       </c>
     </row>
-    <row r="310" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C310" s="2">
         <v>304</v>
       </c>
@@ -11682,7 +11688,7 @@
         <v>34080</v>
       </c>
     </row>
-    <row r="311" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C311" s="2">
         <v>305</v>
       </c>
@@ -11699,7 +11705,7 @@
         <v>239368</v>
       </c>
     </row>
-    <row r="312" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C312" s="2">
         <v>306</v>
       </c>
@@ -11716,7 +11722,7 @@
         <v>86076</v>
       </c>
     </row>
-    <row r="313" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C313" s="2">
         <v>307</v>
       </c>
@@ -11750,7 +11756,7 @@
         <v>-39689</v>
       </c>
     </row>
-    <row r="315" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C315" s="2">
         <v>309</v>
       </c>
@@ -11801,7 +11807,7 @@
         <v>176652</v>
       </c>
     </row>
-    <row r="318" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="3:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C318" s="2">
         <v>312</v>
       </c>
@@ -12515,6 +12521,11 @@
     <row r="997" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="998" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
+  <autoFilter ref="C6:G319" xr:uid="{00000000-0001-0000-0100-000000000000}">
+    <filterColumn colId="3">
+      <dynamicFilter type="Q3"/>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -17874,4 +17885,2600 @@
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77ACB3AA-7844-4687-9CC4-3A116C27575E}">
+  <dimension ref="A1:E68"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="4" max="4" width="10.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="2">
+        <v>2</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="4">
+        <v>44470</v>
+      </c>
+      <c r="E2" s="3">
+        <v>165656</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="2">
+        <v>3</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="4">
+        <v>44256</v>
+      </c>
+      <c r="E3" s="3">
+        <v>25467</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
+        <v>5</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="4">
+        <v>44440</v>
+      </c>
+      <c r="E4" s="3">
+        <v>135801</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
+        <v>13</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="4">
+        <v>44531</v>
+      </c>
+      <c r="E5" s="3">
+        <v>201069</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
+        <v>25</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="4">
+        <v>44440</v>
+      </c>
+      <c r="E6" s="3">
+        <v>60921</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
+        <v>26</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="4">
+        <v>44197</v>
+      </c>
+      <c r="E7" s="3">
+        <v>180969</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
+        <v>31</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="4">
+        <v>44409</v>
+      </c>
+      <c r="E8" s="3">
+        <v>87532</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <v>32</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="4">
+        <v>44531</v>
+      </c>
+      <c r="E9" s="3">
+        <v>82089</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
+        <v>34</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="4">
+        <v>44378</v>
+      </c>
+      <c r="E10" s="3">
+        <v>57399</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
+        <v>47</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="4">
+        <v>44197</v>
+      </c>
+      <c r="E11" s="2">
+        <v>48442</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="2">
+        <v>49</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="4">
+        <v>44501</v>
+      </c>
+      <c r="E12" s="2">
+        <v>146394</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="2">
+        <v>56</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="4">
+        <v>44348</v>
+      </c>
+      <c r="E13" s="2">
+        <v>137843</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="2">
+        <v>57</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="4">
+        <v>44378</v>
+      </c>
+      <c r="E14" s="2">
+        <v>96209</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="2">
+        <v>63</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="4">
+        <v>44348</v>
+      </c>
+      <c r="E15" s="2">
+        <v>7110</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="2">
+        <v>79</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="4">
+        <v>44348</v>
+      </c>
+      <c r="E16" s="2">
+        <v>234786</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="2">
+        <v>83</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="4">
+        <v>44501</v>
+      </c>
+      <c r="E17" s="2">
+        <v>25301</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="2">
+        <v>89</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" s="4">
+        <v>44501</v>
+      </c>
+      <c r="E18" s="2">
+        <v>211082</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="2">
+        <v>95</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="4">
+        <v>44470</v>
+      </c>
+      <c r="E19" s="2">
+        <v>13328</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="2">
+        <v>97</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" s="4">
+        <v>44317</v>
+      </c>
+      <c r="E20" s="2">
+        <v>258583</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="2">
+        <v>99</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" s="4">
+        <v>44440</v>
+      </c>
+      <c r="E21" s="2">
+        <v>147727</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="2">
+        <v>100</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" s="4">
+        <v>44409</v>
+      </c>
+      <c r="E22" s="2">
+        <v>109849</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="2">
+        <v>101</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" s="4">
+        <v>44470</v>
+      </c>
+      <c r="E23" s="2">
+        <v>231047</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="2">
+        <v>113</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="4">
+        <v>44378</v>
+      </c>
+      <c r="E24" s="2">
+        <v>26819</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="2">
+        <v>114</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" s="4">
+        <v>44348</v>
+      </c>
+      <c r="E25" s="2">
+        <v>139728</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="2">
+        <v>117</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="4">
+        <v>44317</v>
+      </c>
+      <c r="E26" s="2">
+        <v>57755</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="2">
+        <v>123</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" s="4">
+        <v>44348</v>
+      </c>
+      <c r="E27" s="2">
+        <v>115261</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="2">
+        <v>125</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D28" s="4">
+        <v>44531</v>
+      </c>
+      <c r="E28" s="2">
+        <v>9682</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" s="2">
+        <v>133</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D29" s="4">
+        <v>44197</v>
+      </c>
+      <c r="E29" s="2">
+        <v>142596</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" s="2">
+        <v>134</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D30" s="4">
+        <v>44348</v>
+      </c>
+      <c r="E30" s="2">
+        <v>165992</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" s="2">
+        <v>138</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31" s="4">
+        <v>44378</v>
+      </c>
+      <c r="E31" s="2">
+        <v>44394</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" s="2">
+        <v>144</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D32" s="4">
+        <v>44287</v>
+      </c>
+      <c r="E32" s="2">
+        <v>35096</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" s="2">
+        <v>151</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D33" s="4">
+        <v>44378</v>
+      </c>
+      <c r="E33" s="2">
+        <v>173616</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" s="2">
+        <v>156</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D34" s="4">
+        <v>44348</v>
+      </c>
+      <c r="E34" s="2">
+        <v>95791</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35" s="2">
+        <v>164</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D35" s="4">
+        <v>44531</v>
+      </c>
+      <c r="E35" s="2">
+        <v>112636</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36" s="2">
+        <v>167</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D36" s="4">
+        <v>44317</v>
+      </c>
+      <c r="E36" s="2">
+        <v>223042</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37" s="2">
+        <v>168</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D37" s="4">
+        <v>44378</v>
+      </c>
+      <c r="E37" s="2">
+        <v>185869</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A38" s="2">
+        <v>169</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D38" s="4">
+        <v>44287</v>
+      </c>
+      <c r="E38" s="2">
+        <v>73394</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A39" s="2">
+        <v>170</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D39" s="4">
+        <v>44348</v>
+      </c>
+      <c r="E39" s="2">
+        <v>254580</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A40" s="2">
+        <v>176</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D40" s="4">
+        <v>44287</v>
+      </c>
+      <c r="E40" s="2">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A41" s="2">
+        <v>182</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D41" s="4">
+        <v>44317</v>
+      </c>
+      <c r="E41" s="2">
+        <v>164464</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A42" s="2">
+        <v>189</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D42" s="4">
+        <v>44228</v>
+      </c>
+      <c r="E42" s="2">
+        <v>210276</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A43" s="2">
+        <v>190</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D43" s="4">
+        <v>44228</v>
+      </c>
+      <c r="E43" s="2">
+        <v>86142</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A44" s="2">
+        <v>203</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D44" s="4">
+        <v>44531</v>
+      </c>
+      <c r="E44" s="2">
+        <v>71529</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A45" s="2">
+        <v>207</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D45" s="4">
+        <v>44440</v>
+      </c>
+      <c r="E45" s="2">
+        <v>258051</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A46" s="2">
+        <v>217</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D46" s="4">
+        <v>44348</v>
+      </c>
+      <c r="E46" s="2">
+        <v>159478</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A47" s="2">
+        <v>220</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D47" s="4">
+        <v>44287</v>
+      </c>
+      <c r="E47" s="2">
+        <v>89649</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A48" s="2">
+        <v>221</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D48" s="4">
+        <v>44287</v>
+      </c>
+      <c r="E48" s="2">
+        <v>42319</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A49" s="2">
+        <v>222</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D49" s="4">
+        <v>44317</v>
+      </c>
+      <c r="E49" s="2">
+        <v>1519</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A50" s="2">
+        <v>229</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D50" s="4">
+        <v>44531</v>
+      </c>
+      <c r="E50" s="2">
+        <v>12709</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A51" s="2">
+        <v>231</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D51" s="4">
+        <v>44501</v>
+      </c>
+      <c r="E51" s="2">
+        <v>39271</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A52" s="2">
+        <v>234</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D52" s="4">
+        <v>44470</v>
+      </c>
+      <c r="E52" s="2">
+        <v>236531</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A53" s="2">
+        <v>235</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D53" s="4">
+        <v>44470</v>
+      </c>
+      <c r="E53" s="2">
+        <v>128249</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A54" s="2">
+        <v>236</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D54" s="4">
+        <v>44531</v>
+      </c>
+      <c r="E54" s="2">
+        <v>210352</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A55" s="2">
+        <v>238</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D55" s="4">
+        <v>44256</v>
+      </c>
+      <c r="E55" s="2">
+        <v>117440</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A56" s="2">
+        <v>240</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D56" s="4">
+        <v>44197</v>
+      </c>
+      <c r="E56" s="2">
+        <v>151301</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A57" s="2">
+        <v>248</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D57" s="4">
+        <v>44378</v>
+      </c>
+      <c r="E57" s="2">
+        <v>89802</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A58" s="2">
+        <v>249</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D58" s="4">
+        <v>44409</v>
+      </c>
+      <c r="E58" s="2">
+        <v>23250</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A59" s="2">
+        <v>257</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D59" s="4">
+        <v>44409</v>
+      </c>
+      <c r="E59" s="2">
+        <v>7382</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A60" s="2">
+        <v>261</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D60" s="4">
+        <v>44348</v>
+      </c>
+      <c r="E60" s="2">
+        <v>7190</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A61" s="2">
+        <v>266</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D61" s="4">
+        <v>44228</v>
+      </c>
+      <c r="E61" s="2">
+        <v>134107</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A62" s="2">
+        <v>269</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D62" s="4">
+        <v>44197</v>
+      </c>
+      <c r="E62" s="2">
+        <v>28289</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A63" s="2">
+        <v>274</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D63" s="4">
+        <v>44531</v>
+      </c>
+      <c r="E63" s="2">
+        <v>100956</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A64" s="2">
+        <v>284</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D64" s="4">
+        <v>44501</v>
+      </c>
+      <c r="E64" s="2">
+        <v>195638</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A65" s="2">
+        <v>292</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D65" s="4">
+        <v>44228</v>
+      </c>
+      <c r="E65" s="2">
+        <v>11682</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A66" s="2">
+        <v>306</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D66" s="4">
+        <v>44470</v>
+      </c>
+      <c r="E66" s="2">
+        <v>86076</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A67" s="2">
+        <v>309</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D67" s="4">
+        <v>44287</v>
+      </c>
+      <c r="E67" s="2">
+        <v>51383</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A68" s="2">
+        <v>311</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D68" s="4">
+        <v>44378</v>
+      </c>
+      <c r="E68" s="2">
+        <v>176652</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94A81BEB-DF12-43B3-8C50-826CF9295A9F}">
+  <dimension ref="A1:E83"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.5546875" customWidth="1"/>
+    <col min="3" max="3" width="24.5546875" customWidth="1"/>
+    <col min="4" max="4" width="10.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="2">
+        <v>5</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="4">
+        <v>44440</v>
+      </c>
+      <c r="E2" s="3">
+        <v>135801</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="2">
+        <v>10</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="4">
+        <v>44378</v>
+      </c>
+      <c r="E3" s="3">
+        <v>-34980</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
+        <v>23</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="4">
+        <v>44409</v>
+      </c>
+      <c r="E4" s="3">
+        <v>149617</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
+        <v>25</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="4">
+        <v>44440</v>
+      </c>
+      <c r="E5" s="3">
+        <v>60921</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
+        <v>28</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="4">
+        <v>44378</v>
+      </c>
+      <c r="E6" s="3">
+        <v>12909</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
+        <v>30</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="4">
+        <v>44378</v>
+      </c>
+      <c r="E7" s="3">
+        <v>36046</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
+        <v>31</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="4">
+        <v>44409</v>
+      </c>
+      <c r="E8" s="3">
+        <v>87532</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <v>33</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="4">
+        <v>44440</v>
+      </c>
+      <c r="E9" s="3">
+        <v>242254</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
+        <v>34</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="4">
+        <v>44378</v>
+      </c>
+      <c r="E10" s="3">
+        <v>57399</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
+        <v>36</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="4">
+        <v>44409</v>
+      </c>
+      <c r="E11" s="3">
+        <v>55010</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="2">
+        <v>40</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="4">
+        <v>44409</v>
+      </c>
+      <c r="E12" s="3">
+        <v>86220</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="2">
+        <v>43</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" s="4">
+        <v>44409</v>
+      </c>
+      <c r="E13" s="3">
+        <v>17711</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="2">
+        <v>52</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14" s="4">
+        <v>44378</v>
+      </c>
+      <c r="E14" s="2">
+        <v>5850</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="2">
+        <v>55</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="4">
+        <v>44409</v>
+      </c>
+      <c r="E15" s="2">
+        <v>131983</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="2">
+        <v>57</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="4">
+        <v>44378</v>
+      </c>
+      <c r="E16" s="2">
+        <v>96209</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="2">
+        <v>61</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="4">
+        <v>44409</v>
+      </c>
+      <c r="E17" s="2">
+        <v>19225</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="2">
+        <v>75</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" s="4">
+        <v>44378</v>
+      </c>
+      <c r="E18" s="2">
+        <v>7819</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="2">
+        <v>76</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D19" s="4">
+        <v>44440</v>
+      </c>
+      <c r="E19" s="2">
+        <v>193691</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="2">
+        <v>77</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D20" s="4">
+        <v>44378</v>
+      </c>
+      <c r="E20" s="2">
+        <v>229218</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="2">
+        <v>81</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D21" s="4">
+        <v>44409</v>
+      </c>
+      <c r="E21" s="2">
+        <v>22746</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="2">
+        <v>82</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D22" s="4">
+        <v>44409</v>
+      </c>
+      <c r="E22" s="2">
+        <v>85536</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="2">
+        <v>84</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23" s="4">
+        <v>44378</v>
+      </c>
+      <c r="E23" s="2">
+        <v>152936</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="2">
+        <v>85</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D24" s="4">
+        <v>44409</v>
+      </c>
+      <c r="E24" s="2">
+        <v>124717</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="2">
+        <v>87</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D25" s="4">
+        <v>44409</v>
+      </c>
+      <c r="E25" s="2">
+        <v>99343</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="2">
+        <v>99</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="4">
+        <v>44440</v>
+      </c>
+      <c r="E26" s="2">
+        <v>147727</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="2">
+        <v>100</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" s="4">
+        <v>44409</v>
+      </c>
+      <c r="E27" s="2">
+        <v>109849</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="2">
+        <v>102</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" s="4">
+        <v>44378</v>
+      </c>
+      <c r="E28" s="2">
+        <v>219148</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" s="2">
+        <v>106</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" s="4">
+        <v>44440</v>
+      </c>
+      <c r="E29" s="2">
+        <v>213879</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" s="2">
+        <v>111</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D30" s="4">
+        <v>44378</v>
+      </c>
+      <c r="E30" s="2">
+        <v>36547</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" s="2">
+        <v>113</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31" s="4">
+        <v>44378</v>
+      </c>
+      <c r="E31" s="2">
+        <v>26819</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" s="2">
+        <v>115</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D32" s="4">
+        <v>44440</v>
+      </c>
+      <c r="E32" s="2">
+        <v>220591</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" s="2">
+        <v>118</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D33" s="4">
+        <v>44409</v>
+      </c>
+      <c r="E33" s="2">
+        <v>102572</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" s="2">
+        <v>119</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D34" s="4">
+        <v>44409</v>
+      </c>
+      <c r="E34" s="2">
+        <v>229197</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35" s="2">
+        <v>120</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D35" s="4">
+        <v>44409</v>
+      </c>
+      <c r="E35" s="2">
+        <v>19002</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36" s="2">
+        <v>121</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D36" s="4">
+        <v>44440</v>
+      </c>
+      <c r="E36" s="2">
+        <v>209590</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37" s="2">
+        <v>132</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D37" s="4">
+        <v>44440</v>
+      </c>
+      <c r="E37" s="2">
+        <v>27327</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A38" s="2">
+        <v>138</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D38" s="4">
+        <v>44378</v>
+      </c>
+      <c r="E38" s="2">
+        <v>44394</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A39" s="2">
+        <v>139</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D39" s="4">
+        <v>44440</v>
+      </c>
+      <c r="E39" s="2">
+        <v>217075</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A40" s="2">
+        <v>142</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D40" s="4">
+        <v>44409</v>
+      </c>
+      <c r="E40" s="2">
+        <v>217962</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A41" s="2">
+        <v>145</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D41" s="4">
+        <v>44378</v>
+      </c>
+      <c r="E41" s="2">
+        <v>64755</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A42" s="2">
+        <v>148</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D42" s="4">
+        <v>44409</v>
+      </c>
+      <c r="E42" s="2">
+        <v>191733</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A43" s="2">
+        <v>150</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D43" s="4">
+        <v>44440</v>
+      </c>
+      <c r="E43" s="2">
+        <v>242971</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A44" s="2">
+        <v>151</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D44" s="4">
+        <v>44378</v>
+      </c>
+      <c r="E44" s="2">
+        <v>173616</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A45" s="2">
+        <v>166</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D45" s="4">
+        <v>44378</v>
+      </c>
+      <c r="E45" s="2">
+        <v>23560</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A46" s="2">
+        <v>168</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D46" s="4">
+        <v>44378</v>
+      </c>
+      <c r="E46" s="2">
+        <v>185869</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A47" s="2">
+        <v>187</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D47" s="4">
+        <v>44409</v>
+      </c>
+      <c r="E47" s="2">
+        <v>67090</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A48" s="2">
+        <v>188</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D48" s="4">
+        <v>44440</v>
+      </c>
+      <c r="E48" s="2">
+        <v>13179</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A49" s="2">
+        <v>192</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D49" s="4">
+        <v>44378</v>
+      </c>
+      <c r="E49" s="2">
+        <v>86843</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A50" s="2">
+        <v>196</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D50" s="4">
+        <v>44378</v>
+      </c>
+      <c r="E50" s="2">
+        <v>103592</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A51" s="2">
+        <v>198</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D51" s="4">
+        <v>44378</v>
+      </c>
+      <c r="E51" s="2">
+        <v>138473</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A52" s="2">
+        <v>200</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D52" s="4">
+        <v>44409</v>
+      </c>
+      <c r="E52" s="2">
+        <v>10877</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A53" s="2">
+        <v>201</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D53" s="4">
+        <v>44409</v>
+      </c>
+      <c r="E53" s="2">
+        <v>155980</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A54" s="2">
+        <v>202</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D54" s="4">
+        <v>44409</v>
+      </c>
+      <c r="E54" s="2">
+        <v>23010</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A55" s="2">
+        <v>206</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D55" s="4">
+        <v>44378</v>
+      </c>
+      <c r="E55" s="2">
+        <v>121986</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A56" s="2">
+        <v>207</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D56" s="4">
+        <v>44440</v>
+      </c>
+      <c r="E56" s="2">
+        <v>258051</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A57" s="2">
+        <v>211</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D57" s="4">
+        <v>44440</v>
+      </c>
+      <c r="E57" s="2">
+        <v>160752</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A58" s="2">
+        <v>216</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D58" s="4">
+        <v>44409</v>
+      </c>
+      <c r="E58" s="2">
+        <v>110965</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A59" s="2">
+        <v>223</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D59" s="4">
+        <v>44409</v>
+      </c>
+      <c r="E59" s="2">
+        <v>78549</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A60" s="2">
+        <v>232</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D60" s="4">
+        <v>44440</v>
+      </c>
+      <c r="E60" s="2">
+        <v>208038</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A61" s="2">
+        <v>233</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D61" s="4">
+        <v>44378</v>
+      </c>
+      <c r="E61" s="2">
+        <v>12894</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A62" s="2">
+        <v>239</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D62" s="4">
+        <v>44440</v>
+      </c>
+      <c r="E62" s="2">
+        <v>256402</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A63" s="2">
+        <v>247</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D63" s="4">
+        <v>44440</v>
+      </c>
+      <c r="E63" s="2">
+        <v>261354</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A64" s="2">
+        <v>248</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D64" s="4">
+        <v>44378</v>
+      </c>
+      <c r="E64" s="2">
+        <v>89802</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A65" s="2">
+        <v>249</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D65" s="4">
+        <v>44409</v>
+      </c>
+      <c r="E65" s="2">
+        <v>23250</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A66" s="2">
+        <v>251</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D66" s="4">
+        <v>44378</v>
+      </c>
+      <c r="E66" s="2">
+        <v>52513</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A67" s="2">
+        <v>254</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D67" s="4">
+        <v>44378</v>
+      </c>
+      <c r="E67" s="2">
+        <v>159745</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A68" s="2">
+        <v>257</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D68" s="4">
+        <v>44409</v>
+      </c>
+      <c r="E68" s="2">
+        <v>7382</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A69" s="2">
+        <v>263</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D69" s="4">
+        <v>44440</v>
+      </c>
+      <c r="E69" s="2">
+        <v>200584</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A70" s="2">
+        <v>264</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D70" s="4">
+        <v>44378</v>
+      </c>
+      <c r="E70" s="2">
+        <v>235104</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A71" s="2">
+        <v>265</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D71" s="4">
+        <v>44440</v>
+      </c>
+      <c r="E71" s="2">
+        <v>55991</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A72" s="2">
+        <v>273</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D72" s="4">
+        <v>44378</v>
+      </c>
+      <c r="E72" s="2">
+        <v>104422</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A73" s="2">
+        <v>276</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D73" s="4">
+        <v>44378</v>
+      </c>
+      <c r="E73" s="2">
+        <v>59920</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A74" s="2">
+        <v>282</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D74" s="4">
+        <v>44409</v>
+      </c>
+      <c r="E74" s="2">
+        <v>216458</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A75" s="2">
+        <v>288</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D75" s="4">
+        <v>44378</v>
+      </c>
+      <c r="E75" s="2">
+        <v>226327</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A76" s="2">
+        <v>291</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D76" s="4">
+        <v>44440</v>
+      </c>
+      <c r="E76" s="2">
+        <v>12156</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A77" s="2">
+        <v>298</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D77" s="4">
+        <v>44440</v>
+      </c>
+      <c r="E77" s="2">
+        <v>98246</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A78" s="2">
+        <v>300</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D78" s="4">
+        <v>44440</v>
+      </c>
+      <c r="E78" s="2">
+        <v>74093</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A79" s="2">
+        <v>302</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D79" s="4">
+        <v>44409</v>
+      </c>
+      <c r="E79" s="2">
+        <v>75634</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A80" s="2">
+        <v>308</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D80" s="4">
+        <v>44378</v>
+      </c>
+      <c r="E80" s="2">
+        <v>-39689</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A81" s="2">
+        <v>310</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D81" s="4">
+        <v>44378</v>
+      </c>
+      <c r="E81" s="2">
+        <v>252080</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A82" s="2">
+        <v>311</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D82" s="4">
+        <v>44378</v>
+      </c>
+      <c r="E82" s="2">
+        <v>176652</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A83" s="2">
+        <v>313</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D83" s="4">
+        <v>44409</v>
+      </c>
+      <c r="E83" s="2">
+        <v>7269</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>